--- a/input/汇总_点赞链接.xlsx
+++ b/input/汇总_点赞链接.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="点赞链接" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
   <si>
     <t>编号</t>
   </si>
@@ -35,445 +35,391 @@
     <t>接龙信息</t>
   </si>
   <si>
-    <t>https://m.tb.cn/h.7tyt6VR?tk=HI44U9NeuZt</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GC2hbZ?tk=3xkjU9neGPA</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GQM0SO?tk=FlNrU9lwXcP</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7Gw0U5H?tk=qRczU9O3fJh</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GjVokC?tk=WV1NU9OomWH</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tCuuQt?tk=aZpfU9meux7</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uD7EZl?tk=lZBiU9mlr3s</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uDRSXQ?tk=70y1U9mlmcm</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uDRquj?tk=qT6wU9mOajQ</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GvWZqp?tk=WL8iU9PfuED</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tvzVHO?tk=H3aAU99ROVD</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7twEgjZ?tk=LDPlU9P5ge8</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7twyAxn?tk=aOiZU9PSL8F</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7twrI34?tk=CIphU9PXc8e</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GvNXwa?tk=On2kU9Pqbma</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tD5uQp?tk=j7wpU9PJ2ul</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GjQQrV?tk=6lK6U9PIw9o</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GvoTmf?tk=GJmJU9PIRiV</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uvlZj6?tk=oTPdU9PIl9r</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7Gj99KW?tk=f4wLU9PIvOd</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uHHbL3?tk=s7mGU9jcoG0</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tdjVEk?tk=f9Q9UjFWzVf</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GEVTHZ?tk=lYG9U9lhExv</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uEfq0Y?tk=5hFfU9ljfV4</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GRvUiT?tk=9X9uU9kX8KY</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uuyqYF?tk=Va2hU9kdP1Z</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uFYAMF?tk=fAoDU9kTK1t</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7J9WAAS?tk=pKOYU7328w4</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tw3aj1?tk=8a3lU9ko3ig</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G8jXbo?tk=kOP3U9kqGPN</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uFkFKS?tk=OKo2U9krj9n</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G8k0tB?tk=BN3fU9ks9OG</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GFLGtT?tk=v9M2U9kIMEe</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G8Pi0G?tk=EL9QU9kH3gV</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uFO8DI?tk=otnsU9kHwVT</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G8lmrr?tk=sRs3U9ktCrm</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7twhAkl?tk=9BlSU9kGBBT</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uFLugD?tk=Z20ZU9kwawO</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GGQJwe?tk=29D6U9QPuJ2</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GijsAe?tk=9YaCU9QIGIK</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G71Ttr?tk=mz3AU9jUv1b</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uGNnIf?tk=hTUiU9Qw9vq</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GGxDV3?tk=vihtU9QBy6M</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uuDK8E?tk=JL2gU9kdeB3</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G737go?tk=A5BwU9j7wuq</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7ut13Lh?tk=rWe0U9j8rGE</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tFaXLw?tk=KX0AU9j8jIT</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7ut1QcX?tk=NIhpU9jQK31</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G7fDIU?tk=iAKyU9j91sw</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G7UfdF?tk=uIvrU9j9nVu</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tF0mMO?tk=XesbU9jPhRO</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7utdp11?tk=z0XrU9j9smc</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GHAdo6?tk=sgjYU9j1OOJ</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GGUBej?tk=Q9h5U9Q67Jq</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GHxtr3?tk=YLSnU9ja0B0</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uHKa8W?tk=9XjsU98AxxX</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GHz2Cw?tk=QBPBU9j083I</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GSwAB2?tk=WLawU9jckLJ</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7Gt0haJ?tk=BvxnU9jX4fK</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7turaQi?tk=LQEAU9jdgEd</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GtXZwD?tk=VsXIU9j36pY</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G7cf4T?tk=zxxoU9jgAeO</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GtfKFE?tk=vhSjU9jTBMB</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G6J0HW?tk=AchVU9iyZ8h</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7ushjRq?tk=l3SUU9Rs19m</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7t81Ilz?tk=ov3JUQ1vjXZ</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7Gsq83p?tk=uoLwU9RGaeD</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tGOWXq?tk=OMbKU9RzPoF</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GH0u60?tk=twDuU982puD</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tu2KhT?tk=IaAwU98mZ2t</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uJ573g?tk=bDGYU9SsorQ</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tsiDLq?tk=tyTpU9Svkzc</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7Ggqqdw?tk=Nht4U9SEHa8</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GJEMES?tk=EeUgU9SwNQc</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7Gr6xUD?tk=gDcLU97SivM</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GIWKEm?tk=DuvfU9ieAI2</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tsF4x0?tk=iz1uU97U7I1</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7HpuoQm?tk=wsRQUQ57Hxu</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GI85Si?tk=0QeIU9iQA5G</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tt1emM?tk=dfFoU9iPQxo</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tOmPDZ?tk=FXg4U9WYN87</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tOnUqF?tk=ED9VU9W1ztn</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7ukLpws?tk=iklwU9W216y</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7ukJ8t3?tk=NtycU9W3uT5</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GpicBf?tk=98NzU9T7uFD</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GfUEiQ?tk=zt2NU9TPV0B</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tJN8c6?tk=5vezU96bug9</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tIwTC5?tk=NcuuU9S6Hhe</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GjCb6X?tk=LkSMU9czP0L</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7HLTVg1?tk=nnunUQfEXLr</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G1p2Pz?tk=jOEbU9W0TSP</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7u82rbT?tk=RnETU91rYuK</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GZ2UrU?tk=EjETU91nZbl</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7u84PS0?tk=fp71U91GPzu</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7t94rTC?tk=YXOBU91uZMq</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G8y2wv?tk=8jDDU9ca0Th</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GjgrkD?tk=DOFAU9chA1j</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GRTc9u?tk=FkoGU9Yiyz0</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GRRTdQ?tk=oUJBU9YkmmT</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7u7UN0q?tk=fQYvU90wcDY</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G8VNqS?tk=2pvxU91UyCv</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uRHmeU?tk=UyxCU91T9d7</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G8RuCX?tk=OzMwU91kwzt</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tAX2X5?tk=piKrU9bO5of</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uieVcM?tk=VmjWU9btXMA</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GiuLY9?tk=l8uYU9bDPG4</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7Givzsw?tk=2DtUU9bCS5w</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GRZN10?tk=aygBU9YcXle</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tzkttj?tk=NmXbU90DiQa</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GTdyLA?tk=CyftUQzRoSB</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G7IniX?tk=33HOU90wh5p</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uUPNV3?tk=7h3EUQy3eEl</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7t8PXAg?tk=mcliU9b2F7l</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7u7lsuk?tk=IAZ5U9bd7iT</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tBwZQY?tk=IjSZU90TN1Y</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tRvqi0?tk=8JfVU90lsVM</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G7iSdK?tk=fSgEU90O8Sq</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tyhjIB?tk=eknAU9atWrB</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uh8vf8?tk=eBJMU9Z09is</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GhDGWN?tk=ifafU9Z1A4k</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7timXZp?tk=0cUkU9Z3dpY</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GWTEB5?tk=QbZEUQFn5nN</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GSUZjR?tk=xnk2U9Z9CJ2</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tiE6VX?tk=yblWU9ZQwnF</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G6ApYk?tk=xo6wU9aVV9H</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G1STl3?tk=vXbCUQsNpMZ</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7Gh7Ahz?tk=yZnvU9aMR3e</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tyUAKw?tk=9wZKU9aK58j</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uh2Dfx?tk=73NCU9asjXb</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tiWSlg?tk=jrHGU9aGP3I</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7txqT0W?tk=6SCWUQAYU4W</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7txGE5d?tk=5WnBUQA4NfQ</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tSmaGV?tk=yIc0UQAVKRO</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uTnez8?tk=jA2cUQA4wu5</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uTEaWX?tk=XUiFUQAky6w</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7G6NVrU?tk=JnihUQAsMhJ</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tCiOia?tk=ew8PUQAt9Rs</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7u6gSIl?tk=WwtwUQAB1DZ</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tDXgQF?tk=BFPaUQBPBvL</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7u5EiVZ?tk=l7PHUQBNXXL</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7u5CvVD?tk=KNG1UQBoDNv</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GgCP1y?tk=FyE2UQz3TWa</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7txa5Y2?tk=FzHaUQz7CE7</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7ugF4ib?tk=5kgMUQzkthY</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7tx9mwB?tk=ZBqBUQzD55W</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7GTv9DP?tk=W1PPUQA0GvN</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.7uTig37?tk=OwQyUQA0bpC</t>
+    <t>https://m.tb.cn/h.i6In6qA?tk=jHMF5acY2JA</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.igeAx72?tk=mduGUzrAAXs</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTM53FK?tk=01Ph5acxGCO</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihvTnLs?tk=Q6bl5aXY93M</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTMNbPm?tk=7yQ45aX3r2V</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihuwb0U?tk=kYUg5a1pnaR</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6Id6hV?tk=lMq75a1p4fk</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihuwGGw?tk=dxJx5a1q1Sn</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihuDmp5?tk=sOfc5a1qiDy</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6daDje?tk=cz3L5a1Ke8s</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6daIyL?tk=zAyi5a1JJuV</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTn099g?tk=ShHF5a1LNf5</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6d46p6?tk=U6Jj5a1wWgZ</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTn6MmK?tk=5IQn5a1y65X</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTm9uTP?tk=Nxij5aYXLFo</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTNbuKs?tk=25K55aYraGM</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i62fYhh?tk=hxoh5aYwce0</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTN7Jvy?tk=XIdo5a1Z0U3</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTNiJIZ?tk=wSSD5a1b4dt</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTNiwoT?tk=xOBf5a10GQ7</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6rO9iO?tk=w9SD5a1bPgl</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihu57ON?tk=gGCw5a1YNcf</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i62nVD3?tk=r95n5a1fhZv</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTNpiHv?tk=XvIt5a1UfmK</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6JT0dQ?tk=ceO55abvoBo</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i4DkGpH?tk=yAuJUxEj4cZ</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6Xj4cB?tk=Xqfv5aYXib6</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTmL90m?tk=G8165aY5lCH</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6XLwE0?tk=5elk5aY5Llg</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTmriEx?tk=0oXp5aYhcCA</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihHyeGF?tk=gwql5a0JzlO</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iht5c39?tk=1hES5ab0Ol5</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihti4Pz?tk=VtQt5abW6hr</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihtFCme?tk=5Ueg5aboqpp</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihWvau6?tk=5uOpUAQaV2d</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6cysO7?tk=0xag5aboSoI</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihtxjun?tk=PTw15abpIev</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6J41VS?tk=MRzX5abGgP7</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTm2TFY?tk=zdkw5abGk5X</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihso7mT?tk=gE5E5aZ8Tj1</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6Yw52o?tk=ltYg5aZna8h</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6YzKg0?tk=NSGU5aZIhYm</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i61byrS?tk=MvTc5aZt0t1</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i617dxx?tk=Bvm85a01D06</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6KJdqc?tk=ls7s5a0VMIn</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTlCbqY?tk=iEJh5a0m6vA</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihsbu6s?tk=ZpyS5aax5Tj</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTu1BZr?tk=OX85UAsxs3I</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihs33Bl?tk=ppXk5aZZ57v</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6p9bTn?tk=3iyl5aZbVtR</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6p9ze8?tk=R2kZ5aZbrtT</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6pkuwP?tk=aHu65aZYJKh</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6pPKaH?tk=ciVZ5aZYxIt</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6YiDFq?tk=OXr45aZcCzS</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6pHC4p?tk=ti8B5aZS4zg</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihMkylU?tk=IpnkUAwT1By</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihI4e5O?tk=Bvvn5aacavc</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6bimpr?tk=Z0vm5aa1w1S</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihIfJlE?tk=yUbX5aacE8r</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6LlI5Y?tk=tf9Y5aaXKch</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6b8p2X?tk=IgAl5aaXAKU</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iT90QFd?tk=l2EYUAzKvu4</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6Zy3PV?tk=FA64UAzrrpM</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iT9dMeG?tk=gtTnUAzuirB</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihoMnf9?tk=8nHIUADRfVI</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihrcepy?tk=Mbm7UAzytVl</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iT98oOR?tk=rhr8UAAYI6y</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iT9sPJt?tk=obRuUAAiSbi</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihrOd4E?tk=Cfk2UAAR0Uq</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihrqrjx?tk=v4X0UAANmxg</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iT9z50s?tk=gAZIUAAorTf</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihJbUnR?tk=tszlUABxw9N</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6MjYYM?tk=miiwUAzZZap</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6Z4Ouz?tk=VQLfUAzZCQN</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTQ78cX?tk=uJI8UAzb5KR</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6MkC5d?tk=MjHcUAz17TW</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTQP410?tk=ozKlUAzdliS</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTQOAS4?tk=0YIxUAzVhGs</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6MAIWG?tk=G8tmUAzMmui</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTQzPNB?tk=aAWQUAzoNtf</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihKnoFM?tk=Q83gUAyjuIM</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iT8D047?tk=98ZLUAy9LDL</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihKIUfK?tk=M3rVUAyNPCJ</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i3wrHnC?tk=tAedUE6AUHg</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTAAs8Y?tk=iNZOUAyEGzc</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTjSpxK?tk=ekOdUAyB4Px</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6abZ5N?tk=yrdNUAywV3O</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTjFqby?tk=EYwqUAB8Lb9</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6NmHdE?tk=ypFdUAy4bAs</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihK7czH?tk=8okpUAyee6Q</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6NmyWU?tk=dZiDUAy4zqO</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6NnMmL?tk=QUQ1UAy4Kaz</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihKRGcG?tk=kQJqUAy4rWP</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTARRs4?tk=UoUSUAyUYwY</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTAlOFE?tk=KFI2UAy7Nl8</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6nxUiw?tk=TjloUABlgAQ</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6OsAot?tk=MLLYUAxjPaG</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihLIizg?tk=eCREUAxPct5</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihLHHd6?tk=J74fUAxOtGn</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTiDWgI?tk=zoNUUAxO612</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6mbyHO?tk=SCstUAxsXx2</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTBtQzd?tk=TkVnUAxIs3n</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTRbk9g?tk=5vTQUAxJCDt</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTR3rKI?tk=OFdeUAxvcAM</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6mON1V?tk=m4AUUACVIjW</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTRIySd?tk=hGKwUAC7Rkc</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6iZyB5?tk=4c0EUAsDj0S</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6PCy8C?tk=iOLKUAwL88b</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihMDtmA?tk=1a1kUAwJ4Bx</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihMyXre?tk=NjpdUAwIHVk</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iho3IEQ?tk=HB01UAwzlJC</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iT7QXSA?tk=SBtyUAD2GEN</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iho7Yxf?tk=KoUHUAD3XN9</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihojKAO?tk=PD7jUADVoA4</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTy7MNk?tk=Pdq6UADgSb5</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6OWuXb?tk=BRU1UADFAy5</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6Pc1GR?tk=hKCLUAEFCNA</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6P2t2o?tk=Sgm5UAEC2Wy</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6P2H3h?tk=s0EFUAEwU3N</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6PheS0?tk=wxHUUAwYM5w</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6PSQil?tk=QtHUUAwcqk2</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihMTZAl?tk=rXnrUAwcAU4</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6PJE1p?tk=KsKRUAwjKeY</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTCnaOB?tk=82tpUAw9wZ2</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTCquac?tk=wlfrUAwNALJ</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6PwCKb?tk=B9adUAwn9SQ</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.iTCrTvR?tk=BtR4UAwny4C</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.ihMFKaC?tk=Ft1ZUAwoSSZ</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.i6PCSaL?tk=R1joUAwLTXZ</t>
   </si>
 </sst>
 </file>
@@ -486,7 +432,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -497,13 +443,6 @@
       <sz val="10"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -960,148 +899,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1110,7 +1049,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1430,13 +1371,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C148"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <dimension ref="A1:B130"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="2" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13" customHeight="1" spans="1:3">
+    <row r="1" ht="13" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1444,889 +1385,783 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="15.75" spans="1:3">
+    <row r="2" ht="41.4" spans="1:2">
       <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" ht="15.75" spans="1:3">
+    </row>
+    <row r="3" ht="41.4" spans="1:2">
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" ht="15.75" spans="1:3">
+    </row>
+    <row r="4" ht="41.4" spans="1:2">
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" ht="15.75" spans="1:3">
+    </row>
+    <row r="5" ht="41.4" spans="1:2">
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" ht="15.75" spans="1:3">
+    </row>
+    <row r="6" ht="41.4" spans="1:2">
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" ht="15.75" spans="1:3">
+    </row>
+    <row r="7" ht="41.4" spans="1:2">
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" ht="15.75" spans="1:3">
+    </row>
+    <row r="8" ht="27.6" spans="1:2">
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" ht="15.75" spans="1:3">
+    </row>
+    <row r="9" ht="41.4" spans="1:2">
       <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" ht="15.75" spans="1:3">
+    </row>
+    <row r="10" ht="41.4" spans="1:2">
       <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" ht="15.75" spans="1:3">
+    </row>
+    <row r="11" ht="27.6" spans="1:2">
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" ht="15.75" spans="1:3">
+    </row>
+    <row r="12" ht="27.6" spans="1:2">
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" ht="15.75" spans="1:3">
+    </row>
+    <row r="13" ht="41.4" spans="1:2">
       <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" ht="15.75" spans="1:3">
+    </row>
+    <row r="14" ht="41.4" spans="1:2">
       <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" ht="15.75" spans="1:3">
+    </row>
+    <row r="15" ht="41.4" spans="1:2">
       <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="2"/>
-    </row>
-    <row r="16" ht="15.75" spans="1:3">
+    </row>
+    <row r="16" ht="41.4" spans="1:2">
       <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" ht="15.75" spans="2:3">
+    </row>
+    <row r="17" ht="41.4" spans="2:2">
       <c r="B17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" ht="15.75" spans="2:3">
+    </row>
+    <row r="18" ht="41.4" spans="2:2">
       <c r="B18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" ht="15.75" spans="2:3">
+    </row>
+    <row r="19" ht="41.4" spans="2:2">
       <c r="B19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" ht="15.75" spans="2:3">
+    </row>
+    <row r="20" ht="27.6" spans="2:2">
       <c r="B20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" ht="15.75" spans="2:3">
+    </row>
+    <row r="21" ht="41.4" spans="2:2">
       <c r="B21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" ht="15.75" spans="2:3">
+    </row>
+    <row r="22" ht="41.4" spans="2:2">
       <c r="B22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" ht="15.75" spans="2:3">
+    </row>
+    <row r="23" ht="41.4" spans="2:2">
       <c r="B23" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" ht="15.75" spans="2:3">
+    </row>
+    <row r="24" ht="41.4" spans="2:2">
       <c r="B24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" ht="15.75" spans="2:3">
+    </row>
+    <row r="25" ht="41.4" spans="2:2">
       <c r="B25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" ht="15.75" spans="2:3">
+    </row>
+    <row r="26" ht="41.4" spans="2:2">
       <c r="B26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="2"/>
-    </row>
-    <row r="27" ht="15.75" spans="2:3">
+    </row>
+    <row r="27" ht="41.4" spans="2:2">
       <c r="B27" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="2"/>
-    </row>
-    <row r="28" ht="15.75" spans="2:3">
+    </row>
+    <row r="28" ht="27.6" spans="2:2">
       <c r="B28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" ht="15.75" spans="2:3">
+    </row>
+    <row r="29" ht="41.4" spans="2:2">
       <c r="B29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="2"/>
-    </row>
-    <row r="30" ht="15.75" spans="2:3">
+    </row>
+    <row r="30" ht="27.6" spans="2:2">
       <c r="B30" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="2"/>
-    </row>
-    <row r="31" ht="15.75" spans="2:3">
+    </row>
+    <row r="31" ht="41.4" spans="2:2">
       <c r="B31" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="2"/>
-    </row>
-    <row r="32" ht="15.75" spans="2:3">
+    </row>
+    <row r="32" ht="41.4" spans="2:2">
       <c r="B32" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="2"/>
-    </row>
-    <row r="33" ht="15.75" spans="2:3">
+    </row>
+    <row r="33" ht="27.6" spans="2:2">
       <c r="B33" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="2"/>
-    </row>
-    <row r="34" ht="15.75" spans="2:3">
+    </row>
+    <row r="34" ht="41.4" spans="2:2">
       <c r="B34" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="2"/>
-    </row>
-    <row r="35" ht="15.75" spans="2:3">
+    </row>
+    <row r="35" ht="41.4" spans="2:2">
       <c r="B35" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="2"/>
-    </row>
-    <row r="36" ht="15.75" spans="2:3">
+    </row>
+    <row r="36" ht="41.4" spans="2:2">
       <c r="B36" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="2"/>
-    </row>
-    <row r="37" ht="15.75" spans="2:3">
+    </row>
+    <row r="37" ht="27.6" spans="2:2">
       <c r="B37" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C37" s="2"/>
-    </row>
-    <row r="38" ht="15.75" spans="2:3">
+    </row>
+    <row r="38" ht="27.6" spans="2:2">
       <c r="B38" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="2"/>
-    </row>
-    <row r="39" ht="15.75" spans="2:3">
+    </row>
+    <row r="39" ht="41.4" spans="2:2">
       <c r="B39" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="2"/>
-    </row>
-    <row r="40" ht="15.75" spans="2:3">
+    </row>
+    <row r="40" ht="41.4" spans="2:2">
       <c r="B40" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="2"/>
-    </row>
-    <row r="41" ht="15.75" spans="2:3">
+    </row>
+    <row r="41" ht="41.4" spans="2:2">
       <c r="B41" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="2"/>
-    </row>
-    <row r="42" ht="15.75" spans="2:3">
+    </row>
+    <row r="42" ht="41.4" spans="2:2">
       <c r="B42" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="2"/>
-    </row>
-    <row r="43" ht="15.75" spans="2:3">
+    </row>
+    <row r="43" ht="41.4" spans="2:2">
       <c r="B43" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C43" s="2"/>
-    </row>
-    <row r="44" ht="15.75" spans="2:3">
+    </row>
+    <row r="44" ht="41.4" spans="2:2">
       <c r="B44" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C44" s="2"/>
-    </row>
-    <row r="45" ht="15.75" spans="2:3">
+    </row>
+    <row r="45" ht="41.4" spans="2:2">
       <c r="B45" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="2"/>
-    </row>
-    <row r="46" ht="15.75" spans="2:3">
+    </row>
+    <row r="46" ht="27.6" spans="2:2">
       <c r="B46" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C46" s="2"/>
-    </row>
-    <row r="47" ht="15.75" spans="2:3">
+    </row>
+    <row r="47" ht="27.6" spans="2:2">
       <c r="B47" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C47" s="2"/>
-    </row>
-    <row r="48" ht="15.75" spans="2:3">
+    </row>
+    <row r="48" ht="27.6" spans="2:2">
       <c r="B48" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="2"/>
-    </row>
-    <row r="49" ht="15.75" spans="2:3">
+    </row>
+    <row r="49" ht="41.4" spans="2:2">
       <c r="B49" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C49" s="2"/>
-    </row>
-    <row r="50" ht="15.75" spans="2:3">
+    </row>
+    <row r="50" ht="41.4" spans="2:2">
       <c r="B50" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C50" s="2"/>
-    </row>
-    <row r="51" ht="15.75" spans="2:3">
+    </row>
+    <row r="51" ht="27.6" spans="2:2">
       <c r="B51" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C51" s="2"/>
-    </row>
-    <row r="52" ht="15.75" spans="2:3">
+    </row>
+    <row r="52" ht="41.4" spans="2:2">
       <c r="B52" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C52" s="2"/>
-    </row>
-    <row r="53" ht="15.75" spans="2:3">
+    </row>
+    <row r="53" ht="41.4" spans="2:2">
       <c r="B53" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="2"/>
-    </row>
-    <row r="54" ht="15.75" spans="2:3">
+    </row>
+    <row r="54" ht="27.6" spans="2:2">
       <c r="B54" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C54" s="2"/>
-    </row>
-    <row r="55" ht="15.75" spans="2:3">
+    </row>
+    <row r="55" ht="41.4" spans="2:2">
       <c r="B55" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C55" s="2"/>
-    </row>
-    <row r="56" ht="15.75" spans="2:3">
+    </row>
+    <row r="56" ht="41.4" spans="2:2">
       <c r="B56" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C56" s="2"/>
-    </row>
-    <row r="57" ht="15.75" spans="2:3">
+    </row>
+    <row r="57" ht="41.4" spans="2:2">
       <c r="B57" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C57" s="2"/>
-    </row>
-    <row r="58" ht="15.75" spans="2:3">
+    </row>
+    <row r="58" ht="27.6" spans="2:2">
       <c r="B58" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C58" s="2"/>
-    </row>
-    <row r="59" ht="15.75" spans="2:3">
+    </row>
+    <row r="59" ht="41.4" spans="2:2">
       <c r="B59" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C59" s="2"/>
-    </row>
-    <row r="60" ht="15.75" spans="2:3">
+    </row>
+    <row r="60" ht="27.6" spans="2:2">
       <c r="B60" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C60" s="2"/>
-    </row>
-    <row r="61" ht="15.75" spans="2:3">
+    </row>
+    <row r="61" ht="27.6" spans="2:2">
       <c r="B61" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C61" s="2"/>
-    </row>
-    <row r="62" ht="15.75" spans="2:3">
+    </row>
+    <row r="62" ht="41.4" spans="2:2">
       <c r="B62" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C62" s="2"/>
-    </row>
-    <row r="63" ht="15.75" spans="2:3">
+    </row>
+    <row r="63" ht="41.4" spans="2:2">
       <c r="B63" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C63" s="2"/>
-    </row>
-    <row r="64" ht="15.75" spans="2:3">
+    </row>
+    <row r="64" ht="41.4" spans="2:2">
       <c r="B64" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C64" s="2"/>
-    </row>
-    <row r="65" ht="15.75" spans="2:3">
+    </row>
+    <row r="65" ht="41.4" spans="2:2">
       <c r="B65" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C65" s="2"/>
-    </row>
-    <row r="66" ht="15.75" spans="2:3">
+    </row>
+    <row r="66" ht="41.4" spans="2:2">
       <c r="B66" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C66" s="2"/>
-    </row>
-    <row r="67" ht="15.75" spans="2:3">
+    </row>
+    <row r="67" ht="41.4" spans="2:2">
       <c r="B67" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C67" s="2"/>
-    </row>
-    <row r="68" ht="15.75" spans="2:3">
+    </row>
+    <row r="68" ht="41.4" spans="2:2">
       <c r="B68" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C68" s="2"/>
-    </row>
-    <row r="69" ht="15.75" spans="2:3">
+    </row>
+    <row r="69" ht="27.6" spans="2:2">
       <c r="B69" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C69" s="2"/>
-    </row>
-    <row r="70" ht="15.75" spans="2:3">
+    </row>
+    <row r="70" ht="41.4" spans="2:2">
       <c r="B70" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C70" s="2"/>
-    </row>
-    <row r="71" ht="15.75" spans="2:3">
+    </row>
+    <row r="71" ht="41.4" spans="2:2">
       <c r="B71" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C71" s="2"/>
-    </row>
-    <row r="72" ht="15.75" spans="2:3">
+    </row>
+    <row r="72" ht="41.4" spans="2:2">
       <c r="B72" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C72" s="2"/>
-    </row>
-    <row r="73" ht="15.75" spans="2:3">
+    </row>
+    <row r="73" ht="41.4" spans="2:2">
       <c r="B73" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C73" s="2"/>
-    </row>
-    <row r="74" ht="15.75" spans="2:3">
+    </row>
+    <row r="74" ht="41.4" spans="2:2">
       <c r="B74" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C74" s="2"/>
-    </row>
-    <row r="75" ht="15.75" spans="2:3">
+    </row>
+    <row r="75" ht="41.4" spans="2:2">
       <c r="B75" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C75" s="2"/>
-    </row>
-    <row r="76" ht="15.75" spans="2:3">
+    </row>
+    <row r="76" ht="41.4" spans="2:2">
       <c r="B76" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C76" s="2"/>
-    </row>
-    <row r="77" ht="15.75" spans="2:3">
+    </row>
+    <row r="77" ht="41.4" spans="2:2">
       <c r="B77" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C77" s="2"/>
-    </row>
-    <row r="78" ht="15.75" spans="2:3">
+    </row>
+    <row r="78" ht="27.6" spans="2:2">
       <c r="B78" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C78" s="2"/>
-    </row>
-    <row r="79" ht="15.75" spans="2:3">
+    </row>
+    <row r="79" ht="41.4" spans="2:2">
       <c r="B79" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C79" s="2"/>
-    </row>
-    <row r="80" ht="15.75" spans="2:3">
+    </row>
+    <row r="80" ht="41.4" spans="2:2">
       <c r="B80" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C80" s="2"/>
-    </row>
-    <row r="81" ht="15.75" spans="2:3">
+    </row>
+    <row r="81" ht="41.4" spans="2:2">
       <c r="B81" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C81" s="2"/>
-    </row>
-    <row r="82" ht="15.75" spans="2:3">
+    </row>
+    <row r="82" ht="41.4" spans="2:2">
       <c r="B82" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C82" s="2"/>
-    </row>
-    <row r="83" ht="15.75" spans="2:3">
+    </row>
+    <row r="83" ht="41.4" spans="2:2">
       <c r="B83" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C83" s="2"/>
-    </row>
-    <row r="84" ht="15.75" spans="2:3">
+    </row>
+    <row r="84" ht="41.4" spans="2:2">
       <c r="B84" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C84" s="2"/>
-    </row>
-    <row r="85" ht="15.75" spans="2:3">
+    </row>
+    <row r="85" ht="41.4" spans="2:2">
       <c r="B85" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C85" s="2"/>
-    </row>
-    <row r="86" ht="15.75" spans="2:3">
+    </row>
+    <row r="86" ht="41.4" spans="2:2">
       <c r="B86" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C86" s="2"/>
-    </row>
-    <row r="87" ht="15.75" spans="2:3">
+    </row>
+    <row r="87" ht="41.4" spans="2:2">
       <c r="B87" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C87" s="2"/>
-    </row>
-    <row r="88" ht="15.75" spans="2:3">
+    </row>
+    <row r="88" ht="41.4" spans="2:2">
       <c r="B88" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C88" s="2"/>
-    </row>
-    <row r="89" ht="15.75" spans="2:3">
+    </row>
+    <row r="89" ht="41.4" spans="2:2">
       <c r="B89" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C89" s="2"/>
-    </row>
-    <row r="90" ht="15.75" spans="2:3">
+    </row>
+    <row r="90" ht="41.4" spans="2:2">
       <c r="B90" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C90" s="2"/>
-    </row>
-    <row r="91" ht="15.75" spans="2:3">
+    </row>
+    <row r="91" ht="41.4" spans="2:2">
       <c r="B91" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C91" s="2"/>
-    </row>
-    <row r="92" ht="15.75" spans="2:3">
+    </row>
+    <row r="92" ht="41.4" spans="2:2">
       <c r="B92" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C92" s="2"/>
-    </row>
-    <row r="93" ht="15.75" spans="2:3">
+    </row>
+    <row r="93" ht="41.4" spans="2:2">
       <c r="B93" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C93" s="2"/>
-    </row>
-    <row r="94" ht="15.75" spans="2:3">
+    </row>
+    <row r="94" ht="41.4" spans="2:2">
       <c r="B94" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C94" s="2"/>
-    </row>
-    <row r="95" ht="15.75" spans="2:3">
+    </row>
+    <row r="95" ht="41.4" spans="2:2">
       <c r="B95" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C95" s="2"/>
-    </row>
-    <row r="96" ht="15.75" spans="2:3">
+    </row>
+    <row r="96" ht="27.6" spans="2:2">
       <c r="B96" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C96" s="2"/>
-    </row>
-    <row r="97" ht="15.75" spans="2:3">
+    </row>
+    <row r="97" ht="41.4" spans="2:2">
       <c r="B97" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C97" s="2"/>
-    </row>
-    <row r="98" ht="15.75" spans="2:3">
+    </row>
+    <row r="98" ht="41.4" spans="2:2">
       <c r="B98" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C98" s="2"/>
-    </row>
-    <row r="99" ht="15.75" spans="2:3">
+    </row>
+    <row r="99" ht="27.6" spans="2:2">
       <c r="B99" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C99" s="2"/>
-    </row>
-    <row r="100" ht="15.75" spans="2:3">
+    </row>
+    <row r="100" ht="41.4" spans="2:2">
       <c r="B100" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C100" s="2"/>
-    </row>
-    <row r="101" ht="15.75" spans="2:3">
+    </row>
+    <row r="101" ht="41.4" spans="2:2">
       <c r="B101" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C101" s="2"/>
-    </row>
-    <row r="102" ht="15.75" spans="2:3">
+    </row>
+    <row r="102" ht="41.4" spans="2:2">
       <c r="B102" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C102" s="2"/>
-    </row>
-    <row r="103" ht="15.75" spans="2:3">
+    </row>
+    <row r="103" ht="41.4" spans="2:2">
       <c r="B103" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C103" s="2"/>
-    </row>
-    <row r="104" ht="15.75" spans="2:3">
+    </row>
+    <row r="104" ht="41.4" spans="2:2">
       <c r="B104" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C104" s="2"/>
-    </row>
-    <row r="105" ht="15.75" spans="2:3">
+    </row>
+    <row r="105" ht="41.4" spans="2:2">
       <c r="B105" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C105" s="2"/>
-    </row>
-    <row r="106" ht="15.75" spans="2:3">
+    </row>
+    <row r="106" ht="41.4" spans="2:2">
       <c r="B106" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C106" s="2"/>
-    </row>
-    <row r="107" ht="15.75" spans="2:3">
+    </row>
+    <row r="107" ht="41.4" spans="2:2">
       <c r="B107" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C107" s="2"/>
-    </row>
-    <row r="108" ht="15.75" spans="2:3">
+    </row>
+    <row r="108" ht="27.6" spans="2:2">
       <c r="B108" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C108" s="2"/>
-    </row>
-    <row r="109" ht="15.75" spans="2:3">
+    </row>
+    <row r="109" ht="41.4" spans="2:2">
       <c r="B109" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C109" s="2"/>
-    </row>
-    <row r="110" ht="15.75" spans="2:3">
+    </row>
+    <row r="110" ht="41.4" spans="2:2">
       <c r="B110" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C110" s="2"/>
-    </row>
-    <row r="111" ht="15.75" spans="2:3">
+    </row>
+    <row r="111" ht="41.4" spans="2:2">
       <c r="B111" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C111" s="2"/>
-    </row>
-    <row r="112" ht="15.75" spans="2:3">
+    </row>
+    <row r="112" ht="41.4" spans="2:2">
       <c r="B112" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C112" s="2"/>
-    </row>
-    <row r="113" ht="15.75" spans="2:3">
+    </row>
+    <row r="113" ht="41.4" spans="2:2">
       <c r="B113" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C113" s="2"/>
-    </row>
-    <row r="114" ht="15.75" spans="2:3">
+    </row>
+    <row r="114" ht="41.4" spans="2:2">
       <c r="B114" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C114" s="2"/>
-    </row>
-    <row r="115" ht="15.75" spans="2:3">
+    </row>
+    <row r="115" ht="41.4" spans="2:2">
       <c r="B115" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C115" s="2"/>
-    </row>
-    <row r="116" ht="15.75" spans="2:3">
+    </row>
+    <row r="116" ht="41.4" spans="2:2">
       <c r="B116" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C116" s="2"/>
-    </row>
-    <row r="117" ht="15.75" spans="2:3">
+    </row>
+    <row r="117" ht="41.4" spans="2:2">
       <c r="B117" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C117" s="2"/>
-    </row>
-    <row r="118" ht="15.75" spans="2:3">
+    </row>
+    <row r="118" ht="41.4" spans="2:2">
       <c r="B118" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C118" s="2"/>
-    </row>
-    <row r="119" ht="15.75" spans="2:3">
+    </row>
+    <row r="119" ht="41.4" spans="2:2">
       <c r="B119" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C119" s="2"/>
-    </row>
-    <row r="120" ht="15.75" spans="2:3">
+    </row>
+    <row r="120" ht="41.4" spans="2:2">
       <c r="B120" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C120" s="2"/>
-    </row>
-    <row r="121" ht="15.75" spans="2:3">
+    </row>
+    <row r="121" ht="41.4" spans="2:2">
       <c r="B121" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C121" s="2"/>
-    </row>
-    <row r="122" ht="15.75" spans="2:3">
+    </row>
+    <row r="122" ht="41.4" spans="2:2">
       <c r="B122" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C122" s="2"/>
-    </row>
-    <row r="123" ht="15.75" spans="2:3">
+    </row>
+    <row r="123" ht="41.4" spans="2:2">
       <c r="B123" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C123" s="2"/>
-    </row>
-    <row r="124" ht="15.75" spans="2:3">
+    </row>
+    <row r="124" ht="41.4" spans="2:2">
       <c r="B124" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C124" s="2"/>
-    </row>
-    <row r="125" ht="15.75" spans="2:3">
+    </row>
+    <row r="125" ht="41.4" spans="2:2">
       <c r="B125" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C125" s="2"/>
-    </row>
-    <row r="126" ht="15.75" spans="2:3">
+    </row>
+    <row r="126" ht="41.4" spans="2:2">
       <c r="B126" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C126" s="2"/>
-    </row>
-    <row r="127" ht="15.75" spans="2:3">
+    </row>
+    <row r="127" ht="41.4" spans="2:2">
       <c r="B127" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C127" s="2"/>
-    </row>
-    <row r="128" ht="15.75" spans="2:3">
+    </row>
+    <row r="128" ht="41.4" spans="2:2">
       <c r="B128" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C128" s="2"/>
-    </row>
-    <row r="129" ht="15.75" spans="2:3">
+    </row>
+    <row r="129" ht="41.4" spans="2:2">
       <c r="B129" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C129" s="2"/>
-    </row>
-    <row r="130" ht="15.75" spans="2:3">
+    </row>
+    <row r="130" ht="41.4" spans="2:2">
       <c r="B130" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C130" s="2"/>
-    </row>
-    <row r="131" ht="15.75" spans="2:3">
-      <c r="B131" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C131" s="2"/>
-    </row>
-    <row r="132" ht="15.75" spans="2:3">
-      <c r="B132" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C132" s="2"/>
-    </row>
-    <row r="133" ht="15.75" spans="2:3">
-      <c r="B133" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C133" s="2"/>
-    </row>
-    <row r="134" ht="15.75" spans="2:3">
-      <c r="B134" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C134" s="2"/>
-    </row>
-    <row r="135" ht="15.75" spans="2:3">
-      <c r="B135" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C135" s="2"/>
-    </row>
-    <row r="136" ht="15.75" spans="2:3">
-      <c r="B136" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C136" s="2"/>
-    </row>
-    <row r="137" ht="15.75" spans="2:3">
-      <c r="B137" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C137" s="2"/>
-    </row>
-    <row r="138" ht="15.75" spans="2:3">
-      <c r="B138" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C138" s="2"/>
-    </row>
-    <row r="139" ht="15.75" spans="2:3">
-      <c r="B139" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C139" s="2"/>
-    </row>
-    <row r="140" ht="15.75" spans="2:3">
-      <c r="B140" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C140" s="2"/>
-    </row>
-    <row r="141" ht="15.75" spans="2:3">
-      <c r="B141" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C141" s="2"/>
-    </row>
-    <row r="142" ht="15.75" spans="2:3">
-      <c r="B142" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C142" s="2"/>
-    </row>
-    <row r="143" ht="15.75" spans="2:3">
-      <c r="B143" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C143" s="2"/>
-    </row>
-    <row r="144" ht="15.75" spans="2:3">
-      <c r="B144" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C144" s="2"/>
-    </row>
-    <row r="145" ht="15.75" spans="2:3">
-      <c r="B145" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C145" s="2"/>
-    </row>
-    <row r="146" ht="15.75" spans="2:3">
-      <c r="B146" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C146" s="2"/>
-    </row>
-    <row r="147" ht="15.75" spans="2:3">
-      <c r="B147" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C147" s="2"/>
-    </row>
-    <row r="148" ht="15.75" spans="2:3">
-      <c r="B148" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C148" s="2"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://m.tb.cn/h.i6In6qA?tk=jHMF5acY2JA" tooltip="https://m.tb.cn/h.i6In6qA?tk=jHMF5acY2JA"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://m.tb.cn/h.igeAx72?tk=mduGUzrAAXs" tooltip="https://m.tb.cn/h.igeAx72?tk=mduGUzrAAXs"/>
+    <hyperlink ref="B4" r:id="rId3" display="https://m.tb.cn/h.iTM53FK?tk=01Ph5acxGCO" tooltip="https://m.tb.cn/h.iTM53FK?tk=01Ph5acxGCO"/>
+    <hyperlink ref="B5" r:id="rId4" display="https://m.tb.cn/h.ihvTnLs?tk=Q6bl5aXY93M" tooltip="https://m.tb.cn/h.ihvTnLs?tk=Q6bl5aXY93M"/>
+    <hyperlink ref="B6" r:id="rId5" display="https://m.tb.cn/h.iTMNbPm?tk=7yQ45aX3r2V" tooltip="https://m.tb.cn/h.iTMNbPm?tk=7yQ45aX3r2V"/>
+    <hyperlink ref="B7" r:id="rId6" display="https://m.tb.cn/h.ihuwb0U?tk=kYUg5a1pnaR" tooltip="https://m.tb.cn/h.ihuwb0U?tk=kYUg5a1pnaR"/>
+    <hyperlink ref="B8" r:id="rId7" display="https://m.tb.cn/h.i6Id6hV?tk=lMq75a1p4fk" tooltip="https://m.tb.cn/h.i6Id6hV?tk=lMq75a1p4fk"/>
+    <hyperlink ref="B9" r:id="rId8" display="https://m.tb.cn/h.ihuwGGw?tk=dxJx5a1q1Sn" tooltip="https://m.tb.cn/h.ihuwGGw?tk=dxJx5a1q1Sn"/>
+    <hyperlink ref="B10" r:id="rId9" display="https://m.tb.cn/h.ihuDmp5?tk=sOfc5a1qiDy" tooltip="https://m.tb.cn/h.ihuDmp5?tk=sOfc5a1qiDy"/>
+    <hyperlink ref="B11" r:id="rId10" display="https://m.tb.cn/h.i6daDje?tk=cz3L5a1Ke8s" tooltip="https://m.tb.cn/h.i6daDje?tk=cz3L5a1Ke8s"/>
+    <hyperlink ref="B12" r:id="rId11" display="https://m.tb.cn/h.i6daIyL?tk=zAyi5a1JJuV" tooltip="https://m.tb.cn/h.i6daIyL?tk=zAyi5a1JJuV"/>
+    <hyperlink ref="B13" r:id="rId12" display="https://m.tb.cn/h.iTn099g?tk=ShHF5a1LNf5" tooltip="https://m.tb.cn/h.iTn099g?tk=ShHF5a1LNf5"/>
+    <hyperlink ref="B14" r:id="rId13" display="https://m.tb.cn/h.i6d46p6?tk=U6Jj5a1wWgZ" tooltip="https://m.tb.cn/h.i6d46p6?tk=U6Jj5a1wWgZ"/>
+    <hyperlink ref="B15" r:id="rId14" display="https://m.tb.cn/h.iTn6MmK?tk=5IQn5a1y65X" tooltip="https://m.tb.cn/h.iTn6MmK?tk=5IQn5a1y65X"/>
+    <hyperlink ref="B16" r:id="rId15" display="https://m.tb.cn/h.iTm9uTP?tk=Nxij5aYXLFo" tooltip="https://m.tb.cn/h.iTm9uTP?tk=Nxij5aYXLFo"/>
+    <hyperlink ref="B17" r:id="rId16" display="https://m.tb.cn/h.iTNbuKs?tk=25K55aYraGM" tooltip="https://m.tb.cn/h.iTNbuKs?tk=25K55aYraGM"/>
+    <hyperlink ref="B18" r:id="rId17" display="https://m.tb.cn/h.i62fYhh?tk=hxoh5aYwce0" tooltip="https://m.tb.cn/h.i62fYhh?tk=hxoh5aYwce0"/>
+    <hyperlink ref="B19" r:id="rId18" display="https://m.tb.cn/h.iTN7Jvy?tk=XIdo5a1Z0U3" tooltip="https://m.tb.cn/h.iTN7Jvy?tk=XIdo5a1Z0U3"/>
+    <hyperlink ref="B20" r:id="rId19" display="https://m.tb.cn/h.iTNiJIZ?tk=wSSD5a1b4dt" tooltip="https://m.tb.cn/h.iTNiJIZ?tk=wSSD5a1b4dt"/>
+    <hyperlink ref="B21" r:id="rId20" display="https://m.tb.cn/h.iTNiwoT?tk=xOBf5a10GQ7" tooltip="https://m.tb.cn/h.iTNiwoT?tk=xOBf5a10GQ7"/>
+    <hyperlink ref="B22" r:id="rId21" display="https://m.tb.cn/h.i6rO9iO?tk=w9SD5a1bPgl" tooltip="https://m.tb.cn/h.i6rO9iO?tk=w9SD5a1bPgl"/>
+    <hyperlink ref="B23" r:id="rId22" display="https://m.tb.cn/h.ihu57ON?tk=gGCw5a1YNcf" tooltip="https://m.tb.cn/h.ihu57ON?tk=gGCw5a1YNcf"/>
+    <hyperlink ref="B24" r:id="rId23" display="https://m.tb.cn/h.i62nVD3?tk=r95n5a1fhZv" tooltip="https://m.tb.cn/h.i62nVD3?tk=r95n5a1fhZv"/>
+    <hyperlink ref="B25" r:id="rId24" display="https://m.tb.cn/h.iTNpiHv?tk=XvIt5a1UfmK" tooltip="https://m.tb.cn/h.iTNpiHv?tk=XvIt5a1UfmK"/>
+    <hyperlink ref="B26" r:id="rId25" display="https://m.tb.cn/h.i6JT0dQ?tk=ceO55abvoBo" tooltip="https://m.tb.cn/h.i6JT0dQ?tk=ceO55abvoBo"/>
+    <hyperlink ref="B27" r:id="rId26" display="https://m.tb.cn/h.i4DkGpH?tk=yAuJUxEj4cZ" tooltip="https://m.tb.cn/h.i4DkGpH?tk=yAuJUxEj4cZ"/>
+    <hyperlink ref="B28" r:id="rId27" display="https://m.tb.cn/h.i6Xj4cB?tk=Xqfv5aYXib6" tooltip="https://m.tb.cn/h.i6Xj4cB?tk=Xqfv5aYXib6"/>
+    <hyperlink ref="B29" r:id="rId28" display="https://m.tb.cn/h.iTmL90m?tk=G8165aY5lCH" tooltip="https://m.tb.cn/h.iTmL90m?tk=G8165aY5lCH"/>
+    <hyperlink ref="B30" r:id="rId29" display="https://m.tb.cn/h.i6XLwE0?tk=5elk5aY5Llg" tooltip="https://m.tb.cn/h.i6XLwE0?tk=5elk5aY5Llg"/>
+    <hyperlink ref="B31" r:id="rId30" display="https://m.tb.cn/h.iTmriEx?tk=0oXp5aYhcCA" tooltip="https://m.tb.cn/h.iTmriEx?tk=0oXp5aYhcCA"/>
+    <hyperlink ref="B32" r:id="rId31" display="https://m.tb.cn/h.ihHyeGF?tk=gwql5a0JzlO" tooltip="https://m.tb.cn/h.ihHyeGF?tk=gwql5a0JzlO"/>
+    <hyperlink ref="B33" r:id="rId32" display="https://m.tb.cn/h.iht5c39?tk=1hES5ab0Ol5" tooltip="https://m.tb.cn/h.iht5c39?tk=1hES5ab0Ol5"/>
+    <hyperlink ref="B34" r:id="rId33" display="https://m.tb.cn/h.ihti4Pz?tk=VtQt5abW6hr" tooltip="https://m.tb.cn/h.ihti4Pz?tk=VtQt5abW6hr"/>
+    <hyperlink ref="B35" r:id="rId34" display="https://m.tb.cn/h.ihtFCme?tk=5Ueg5aboqpp" tooltip="https://m.tb.cn/h.ihtFCme?tk=5Ueg5aboqpp"/>
+    <hyperlink ref="B36" r:id="rId35" display="https://m.tb.cn/h.ihWvau6?tk=5uOpUAQaV2d" tooltip="https://m.tb.cn/h.ihWvau6?tk=5uOpUAQaV2d"/>
+    <hyperlink ref="B37" r:id="rId36" display="https://m.tb.cn/h.i6cysO7?tk=0xag5aboSoI" tooltip="https://m.tb.cn/h.i6cysO7?tk=0xag5aboSoI"/>
+    <hyperlink ref="B38" r:id="rId37" display="https://m.tb.cn/h.ihtxjun?tk=PTw15abpIev" tooltip="https://m.tb.cn/h.ihtxjun?tk=PTw15abpIev"/>
+    <hyperlink ref="B39" r:id="rId38" display="https://m.tb.cn/h.i6J41VS?tk=MRzX5abGgP7" tooltip="https://m.tb.cn/h.i6J41VS?tk=MRzX5abGgP7"/>
+    <hyperlink ref="B40" r:id="rId39" display="https://m.tb.cn/h.iTm2TFY?tk=zdkw5abGk5X" tooltip="https://m.tb.cn/h.iTm2TFY?tk=zdkw5abGk5X"/>
+    <hyperlink ref="B41" r:id="rId40" display="https://m.tb.cn/h.ihso7mT?tk=gE5E5aZ8Tj1" tooltip="https://m.tb.cn/h.ihso7mT?tk=gE5E5aZ8Tj1"/>
+    <hyperlink ref="B42" r:id="rId41" display="https://m.tb.cn/h.i6Yw52o?tk=ltYg5aZna8h" tooltip="https://m.tb.cn/h.i6Yw52o?tk=ltYg5aZna8h"/>
+    <hyperlink ref="B43" r:id="rId42" display="https://m.tb.cn/h.i6YzKg0?tk=NSGU5aZIhYm" tooltip="https://m.tb.cn/h.i6YzKg0?tk=NSGU5aZIhYm"/>
+    <hyperlink ref="B44" r:id="rId43" display="https://m.tb.cn/h.i61byrS?tk=MvTc5aZt0t1" tooltip="https://m.tb.cn/h.i61byrS?tk=MvTc5aZt0t1"/>
+    <hyperlink ref="B45" r:id="rId44" display="https://m.tb.cn/h.i617dxx?tk=Bvm85a01D06" tooltip="https://m.tb.cn/h.i617dxx?tk=Bvm85a01D06"/>
+    <hyperlink ref="B46" r:id="rId45" display="https://m.tb.cn/h.i6KJdqc?tk=ls7s5a0VMIn" tooltip="https://m.tb.cn/h.i6KJdqc?tk=ls7s5a0VMIn"/>
+    <hyperlink ref="B47" r:id="rId46" display="https://m.tb.cn/h.iTlCbqY?tk=iEJh5a0m6vA" tooltip="https://m.tb.cn/h.iTlCbqY?tk=iEJh5a0m6vA"/>
+    <hyperlink ref="B48" r:id="rId47" display="https://m.tb.cn/h.ihsbu6s?tk=ZpyS5aax5Tj" tooltip="https://m.tb.cn/h.ihsbu6s?tk=ZpyS5aax5Tj"/>
+    <hyperlink ref="B49" r:id="rId48" display="https://m.tb.cn/h.iTu1BZr?tk=OX85UAsxs3I" tooltip="https://m.tb.cn/h.iTu1BZr?tk=OX85UAsxs3I"/>
+    <hyperlink ref="B50" r:id="rId49" display="https://m.tb.cn/h.ihs33Bl?tk=ppXk5aZZ57v" tooltip="https://m.tb.cn/h.ihs33Bl?tk=ppXk5aZZ57v"/>
+    <hyperlink ref="B51" r:id="rId50" display="https://m.tb.cn/h.i6p9bTn?tk=3iyl5aZbVtR" tooltip="https://m.tb.cn/h.i6p9bTn?tk=3iyl5aZbVtR"/>
+    <hyperlink ref="B52" r:id="rId51" display="https://m.tb.cn/h.i6p9ze8?tk=R2kZ5aZbrtT" tooltip="https://m.tb.cn/h.i6p9ze8?tk=R2kZ5aZbrtT"/>
+    <hyperlink ref="B53" r:id="rId52" display="https://m.tb.cn/h.i6pkuwP?tk=aHu65aZYJKh" tooltip="https://m.tb.cn/h.i6pkuwP?tk=aHu65aZYJKh"/>
+    <hyperlink ref="B54" r:id="rId53" display="https://m.tb.cn/h.i6pPKaH?tk=ciVZ5aZYxIt" tooltip="https://m.tb.cn/h.i6pPKaH?tk=ciVZ5aZYxIt"/>
+    <hyperlink ref="B55" r:id="rId54" display="https://m.tb.cn/h.i6YiDFq?tk=OXr45aZcCzS" tooltip="https://m.tb.cn/h.i6YiDFq?tk=OXr45aZcCzS"/>
+    <hyperlink ref="B56" r:id="rId55" display="https://m.tb.cn/h.i6pHC4p?tk=ti8B5aZS4zg" tooltip="https://m.tb.cn/h.i6pHC4p?tk=ti8B5aZS4zg"/>
+    <hyperlink ref="B57" r:id="rId56" display="https://m.tb.cn/h.ihMkylU?tk=IpnkUAwT1By" tooltip="https://m.tb.cn/h.ihMkylU?tk=IpnkUAwT1By"/>
+    <hyperlink ref="B58" r:id="rId57" display="https://m.tb.cn/h.ihI4e5O?tk=Bvvn5aacavc" tooltip="https://m.tb.cn/h.ihI4e5O?tk=Bvvn5aacavc"/>
+    <hyperlink ref="B59" r:id="rId58" display="https://m.tb.cn/h.i6bimpr?tk=Z0vm5aa1w1S" tooltip="https://m.tb.cn/h.i6bimpr?tk=Z0vm5aa1w1S"/>
+    <hyperlink ref="B60" r:id="rId59" display="https://m.tb.cn/h.ihIfJlE?tk=yUbX5aacE8r" tooltip="https://m.tb.cn/h.ihIfJlE?tk=yUbX5aacE8r"/>
+    <hyperlink ref="B61" r:id="rId60" display="https://m.tb.cn/h.i6LlI5Y?tk=tf9Y5aaXKch" tooltip="https://m.tb.cn/h.i6LlI5Y?tk=tf9Y5aaXKch"/>
+    <hyperlink ref="B62" r:id="rId61" display="https://m.tb.cn/h.i6b8p2X?tk=IgAl5aaXAKU" tooltip="https://m.tb.cn/h.i6b8p2X?tk=IgAl5aaXAKU"/>
+    <hyperlink ref="B63" r:id="rId62" display="https://m.tb.cn/h.iT90QFd?tk=l2EYUAzKvu4" tooltip="https://m.tb.cn/h.iT90QFd?tk=l2EYUAzKvu4"/>
+    <hyperlink ref="B64" r:id="rId63" display="https://m.tb.cn/h.i6Zy3PV?tk=FA64UAzrrpM" tooltip="https://m.tb.cn/h.i6Zy3PV?tk=FA64UAzrrpM"/>
+    <hyperlink ref="B65" r:id="rId64" display="https://m.tb.cn/h.iT9dMeG?tk=gtTnUAzuirB" tooltip="https://m.tb.cn/h.iT9dMeG?tk=gtTnUAzuirB"/>
+    <hyperlink ref="B66" r:id="rId65" display="https://m.tb.cn/h.ihoMnf9?tk=8nHIUADRfVI" tooltip="https://m.tb.cn/h.ihoMnf9?tk=8nHIUADRfVI"/>
+    <hyperlink ref="B67" r:id="rId66" display="https://m.tb.cn/h.ihrcepy?tk=Mbm7UAzytVl" tooltip="https://m.tb.cn/h.ihrcepy?tk=Mbm7UAzytVl"/>
+    <hyperlink ref="B68" r:id="rId67" display="https://m.tb.cn/h.iT98oOR?tk=rhr8UAAYI6y" tooltip="https://m.tb.cn/h.iT98oOR?tk=rhr8UAAYI6y"/>
+    <hyperlink ref="B69" r:id="rId68" display="https://m.tb.cn/h.iT9sPJt?tk=obRuUAAiSbi" tooltip="https://m.tb.cn/h.iT9sPJt?tk=obRuUAAiSbi"/>
+    <hyperlink ref="B70" r:id="rId69" display="https://m.tb.cn/h.ihrOd4E?tk=Cfk2UAAR0Uq" tooltip="https://m.tb.cn/h.ihrOd4E?tk=Cfk2UAAR0Uq"/>
+    <hyperlink ref="B71" r:id="rId70" display="https://m.tb.cn/h.ihrqrjx?tk=v4X0UAANmxg" tooltip="https://m.tb.cn/h.ihrqrjx?tk=v4X0UAANmxg"/>
+    <hyperlink ref="B72" r:id="rId71" display="https://m.tb.cn/h.iT9z50s?tk=gAZIUAAorTf" tooltip="https://m.tb.cn/h.iT9z50s?tk=gAZIUAAorTf"/>
+    <hyperlink ref="B73" r:id="rId72" display="https://m.tb.cn/h.ihJbUnR?tk=tszlUABxw9N" tooltip="https://m.tb.cn/h.ihJbUnR?tk=tszlUABxw9N"/>
+    <hyperlink ref="B74" r:id="rId73" display="https://m.tb.cn/h.i6MjYYM?tk=miiwUAzZZap" tooltip="https://m.tb.cn/h.i6MjYYM?tk=miiwUAzZZap"/>
+    <hyperlink ref="B75" r:id="rId74" display="https://m.tb.cn/h.i6Z4Ouz?tk=VQLfUAzZCQN" tooltip="https://m.tb.cn/h.i6Z4Ouz?tk=VQLfUAzZCQN"/>
+    <hyperlink ref="B76" r:id="rId75" display="https://m.tb.cn/h.iTQ78cX?tk=uJI8UAzb5KR" tooltip="https://m.tb.cn/h.iTQ78cX?tk=uJI8UAzb5KR"/>
+    <hyperlink ref="B77" r:id="rId76" display="https://m.tb.cn/h.i6MkC5d?tk=MjHcUAz17TW" tooltip="https://m.tb.cn/h.i6MkC5d?tk=MjHcUAz17TW"/>
+    <hyperlink ref="B78" r:id="rId77" display="https://m.tb.cn/h.iTQP410?tk=ozKlUAzdliS" tooltip="https://m.tb.cn/h.iTQP410?tk=ozKlUAzdliS"/>
+    <hyperlink ref="B79" r:id="rId78" display="https://m.tb.cn/h.iTQOAS4?tk=0YIxUAzVhGs" tooltip="https://m.tb.cn/h.iTQOAS4?tk=0YIxUAzVhGs"/>
+    <hyperlink ref="B80" r:id="rId79" display="https://m.tb.cn/h.i6MAIWG?tk=G8tmUAzMmui" tooltip="https://m.tb.cn/h.i6MAIWG?tk=G8tmUAzMmui"/>
+    <hyperlink ref="B81" r:id="rId80" display="https://m.tb.cn/h.iTQzPNB?tk=aAWQUAzoNtf" tooltip="https://m.tb.cn/h.iTQzPNB?tk=aAWQUAzoNtf"/>
+    <hyperlink ref="B82" r:id="rId81" display="https://m.tb.cn/h.ihKnoFM?tk=Q83gUAyjuIM" tooltip="https://m.tb.cn/h.ihKnoFM?tk=Q83gUAyjuIM"/>
+    <hyperlink ref="B83" r:id="rId82" display="https://m.tb.cn/h.iT8D047?tk=98ZLUAy9LDL" tooltip="https://m.tb.cn/h.iT8D047?tk=98ZLUAy9LDL"/>
+    <hyperlink ref="B84" r:id="rId83" display="https://m.tb.cn/h.ihKIUfK?tk=M3rVUAyNPCJ" tooltip="https://m.tb.cn/h.ihKIUfK?tk=M3rVUAyNPCJ"/>
+    <hyperlink ref="B85" r:id="rId84" display="https://m.tb.cn/h.i3wrHnC?tk=tAedUE6AUHg" tooltip="https://m.tb.cn/h.i3wrHnC?tk=tAedUE6AUHg"/>
+    <hyperlink ref="B86" r:id="rId85" display="https://m.tb.cn/h.iTAAs8Y?tk=iNZOUAyEGzc" tooltip="https://m.tb.cn/h.iTAAs8Y?tk=iNZOUAyEGzc"/>
+    <hyperlink ref="B87" r:id="rId86" display="https://m.tb.cn/h.iTjSpxK?tk=ekOdUAyB4Px" tooltip="https://m.tb.cn/h.iTjSpxK?tk=ekOdUAyB4Px"/>
+    <hyperlink ref="B88" r:id="rId87" display="https://m.tb.cn/h.i6abZ5N?tk=yrdNUAywV3O" tooltip="https://m.tb.cn/h.i6abZ5N?tk=yrdNUAywV3O"/>
+    <hyperlink ref="B89" r:id="rId88" display="https://m.tb.cn/h.iTjFqby?tk=EYwqUAB8Lb9" tooltip="https://m.tb.cn/h.iTjFqby?tk=EYwqUAB8Lb9"/>
+    <hyperlink ref="B90" r:id="rId89" display="https://m.tb.cn/h.i6NmHdE?tk=ypFdUAy4bAs" tooltip="https://m.tb.cn/h.i6NmHdE?tk=ypFdUAy4bAs"/>
+    <hyperlink ref="B91" r:id="rId90" display="https://m.tb.cn/h.ihK7czH?tk=8okpUAyee6Q" tooltip="https://m.tb.cn/h.ihK7czH?tk=8okpUAyee6Q"/>
+    <hyperlink ref="B92" r:id="rId91" display="https://m.tb.cn/h.i6NmyWU?tk=dZiDUAy4zqO" tooltip="https://m.tb.cn/h.i6NmyWU?tk=dZiDUAy4zqO"/>
+    <hyperlink ref="B93" r:id="rId92" display="https://m.tb.cn/h.i6NnMmL?tk=QUQ1UAy4Kaz" tooltip="https://m.tb.cn/h.i6NnMmL?tk=QUQ1UAy4Kaz"/>
+    <hyperlink ref="B94" r:id="rId93" display="https://m.tb.cn/h.ihKRGcG?tk=kQJqUAy4rWP" tooltip="https://m.tb.cn/h.ihKRGcG?tk=kQJqUAy4rWP"/>
+    <hyperlink ref="B95" r:id="rId94" display="https://m.tb.cn/h.iTARRs4?tk=UoUSUAyUYwY" tooltip="https://m.tb.cn/h.iTARRs4?tk=UoUSUAyUYwY"/>
+    <hyperlink ref="B96" r:id="rId95" display="https://m.tb.cn/h.iTAlOFE?tk=KFI2UAy7Nl8" tooltip="https://m.tb.cn/h.iTAlOFE?tk=KFI2UAy7Nl8"/>
+    <hyperlink ref="B97" r:id="rId96" display="https://m.tb.cn/h.i6nxUiw?tk=TjloUABlgAQ" tooltip="https://m.tb.cn/h.i6nxUiw?tk=TjloUABlgAQ"/>
+    <hyperlink ref="B98" r:id="rId97" display="https://m.tb.cn/h.i6OsAot?tk=MLLYUAxjPaG" tooltip="https://m.tb.cn/h.i6OsAot?tk=MLLYUAxjPaG"/>
+    <hyperlink ref="B99" r:id="rId98" display="https://m.tb.cn/h.ihLIizg?tk=eCREUAxPct5" tooltip="https://m.tb.cn/h.ihLIizg?tk=eCREUAxPct5"/>
+    <hyperlink ref="B100" r:id="rId99" display="https://m.tb.cn/h.ihLHHd6?tk=J74fUAxOtGn" tooltip="https://m.tb.cn/h.ihLHHd6?tk=J74fUAxOtGn"/>
+    <hyperlink ref="B101" r:id="rId100" display="https://m.tb.cn/h.iTiDWgI?tk=zoNUUAxO612" tooltip="https://m.tb.cn/h.iTiDWgI?tk=zoNUUAxO612"/>
+    <hyperlink ref="B102" r:id="rId101" display="https://m.tb.cn/h.i6mbyHO?tk=SCstUAxsXx2" tooltip="https://m.tb.cn/h.i6mbyHO?tk=SCstUAxsXx2"/>
+    <hyperlink ref="B103" r:id="rId102" display="https://m.tb.cn/h.iTBtQzd?tk=TkVnUAxIs3n" tooltip="https://m.tb.cn/h.iTBtQzd?tk=TkVnUAxIs3n"/>
+    <hyperlink ref="B104" r:id="rId103" display="https://m.tb.cn/h.iTRbk9g?tk=5vTQUAxJCDt" tooltip="https://m.tb.cn/h.iTRbk9g?tk=5vTQUAxJCDt"/>
+    <hyperlink ref="B105" r:id="rId104" display="https://m.tb.cn/h.iTR3rKI?tk=OFdeUAxvcAM" tooltip="https://m.tb.cn/h.iTR3rKI?tk=OFdeUAxvcAM"/>
+    <hyperlink ref="B106" r:id="rId105" display="https://m.tb.cn/h.i6mON1V?tk=m4AUUACVIjW" tooltip="https://m.tb.cn/h.i6mON1V?tk=m4AUUACVIjW"/>
+    <hyperlink ref="B107" r:id="rId106" display="https://m.tb.cn/h.iTRIySd?tk=hGKwUAC7Rkc" tooltip="https://m.tb.cn/h.iTRIySd?tk=hGKwUAC7Rkc"/>
+    <hyperlink ref="B108" r:id="rId107" display="https://m.tb.cn/h.i6iZyB5?tk=4c0EUAsDj0S" tooltip="https://m.tb.cn/h.i6iZyB5?tk=4c0EUAsDj0S"/>
+    <hyperlink ref="B109" r:id="rId108" display="https://m.tb.cn/h.i6PCy8C?tk=iOLKUAwL88b" tooltip="https://m.tb.cn/h.i6PCy8C?tk=iOLKUAwL88b"/>
+    <hyperlink ref="B110" r:id="rId109" display="https://m.tb.cn/h.ihMDtmA?tk=1a1kUAwJ4Bx" tooltip="https://m.tb.cn/h.ihMDtmA?tk=1a1kUAwJ4Bx"/>
+    <hyperlink ref="B111" r:id="rId110" display="https://m.tb.cn/h.ihMyXre?tk=NjpdUAwIHVk" tooltip="https://m.tb.cn/h.ihMyXre?tk=NjpdUAwIHVk"/>
+    <hyperlink ref="B112" r:id="rId111" display="https://m.tb.cn/h.iho3IEQ?tk=HB01UAwzlJC" tooltip="https://m.tb.cn/h.iho3IEQ?tk=HB01UAwzlJC"/>
+    <hyperlink ref="B113" r:id="rId112" display="https://m.tb.cn/h.iT7QXSA?tk=SBtyUAD2GEN" tooltip="https://m.tb.cn/h.iT7QXSA?tk=SBtyUAD2GEN"/>
+    <hyperlink ref="B114" r:id="rId113" display="https://m.tb.cn/h.iho7Yxf?tk=KoUHUAD3XN9" tooltip="https://m.tb.cn/h.iho7Yxf?tk=KoUHUAD3XN9"/>
+    <hyperlink ref="B115" r:id="rId114" display="https://m.tb.cn/h.ihojKAO?tk=PD7jUADVoA4" tooltip="https://m.tb.cn/h.ihojKAO?tk=PD7jUADVoA4"/>
+    <hyperlink ref="B116" r:id="rId115" display="https://m.tb.cn/h.iTy7MNk?tk=Pdq6UADgSb5" tooltip="https://m.tb.cn/h.iTy7MNk?tk=Pdq6UADgSb5"/>
+    <hyperlink ref="B117" r:id="rId116" display="https://m.tb.cn/h.i6OWuXb?tk=BRU1UADFAy5" tooltip="https://m.tb.cn/h.i6OWuXb?tk=BRU1UADFAy5"/>
+    <hyperlink ref="B118" r:id="rId117" display="https://m.tb.cn/h.i6Pc1GR?tk=hKCLUAEFCNA" tooltip="https://m.tb.cn/h.i6Pc1GR?tk=hKCLUAEFCNA"/>
+    <hyperlink ref="B119" r:id="rId118" display="https://m.tb.cn/h.i6P2t2o?tk=Sgm5UAEC2Wy" tooltip="https://m.tb.cn/h.i6P2t2o?tk=Sgm5UAEC2Wy"/>
+    <hyperlink ref="B120" r:id="rId119" display="https://m.tb.cn/h.i6P2H3h?tk=s0EFUAEwU3N" tooltip="https://m.tb.cn/h.i6P2H3h?tk=s0EFUAEwU3N"/>
+    <hyperlink ref="B121" r:id="rId120" display="https://m.tb.cn/h.i6PheS0?tk=wxHUUAwYM5w" tooltip="https://m.tb.cn/h.i6PheS0?tk=wxHUUAwYM5w"/>
+    <hyperlink ref="B122" r:id="rId121" display="https://m.tb.cn/h.i6PSQil?tk=QtHUUAwcqk2" tooltip="https://m.tb.cn/h.i6PSQil?tk=QtHUUAwcqk2"/>
+    <hyperlink ref="B123" r:id="rId122" display="https://m.tb.cn/h.ihMTZAl?tk=rXnrUAwcAU4" tooltip="https://m.tb.cn/h.ihMTZAl?tk=rXnrUAwcAU4"/>
+    <hyperlink ref="B124" r:id="rId123" display="https://m.tb.cn/h.i6PJE1p?tk=KsKRUAwjKeY" tooltip="https://m.tb.cn/h.i6PJE1p?tk=KsKRUAwjKeY"/>
+    <hyperlink ref="B125" r:id="rId124" display="https://m.tb.cn/h.iTCnaOB?tk=82tpUAw9wZ2" tooltip="https://m.tb.cn/h.iTCnaOB?tk=82tpUAw9wZ2"/>
+    <hyperlink ref="B126" r:id="rId125" display="https://m.tb.cn/h.iTCquac?tk=wlfrUAwNALJ" tooltip="https://m.tb.cn/h.iTCquac?tk=wlfrUAwNALJ"/>
+    <hyperlink ref="B127" r:id="rId126" display="https://m.tb.cn/h.i6PwCKb?tk=B9adUAwn9SQ" tooltip="https://m.tb.cn/h.i6PwCKb?tk=B9adUAwn9SQ"/>
+    <hyperlink ref="B128" r:id="rId127" display="https://m.tb.cn/h.iTCrTvR?tk=BtR4UAwny4C" tooltip="https://m.tb.cn/h.iTCrTvR?tk=BtR4UAwny4C"/>
+    <hyperlink ref="B129" r:id="rId128" display="https://m.tb.cn/h.ihMFKaC?tk=Ft1ZUAwoSSZ" tooltip="https://m.tb.cn/h.ihMFKaC?tk=Ft1ZUAwoSSZ"/>
+    <hyperlink ref="B130" r:id="rId129" display="https://m.tb.cn/h.i6PCSaL?tk=R1joUAwLTXZ" tooltip="https://m.tb.cn/h.i6PCSaL?tk=R1joUAwLTXZ"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
